--- a/137554_Cuenca_Rimac/_raw_reportes_xlsx/IDConfig_64971_completo.xlsx
+++ b/137554_Cuenca_Rimac/_raw_reportes_xlsx/IDConfig_64971_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R5cae2042b4084469"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rb9106c0a941c4115"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
       </x:c>
       <x:c s="" t="inlineStr">
         <x:is>
-          <x:t>Dpto: Lima / Prov: Huarochiri / Dist.: San Mateo</x:t>
+          <x:t>Dpto: Lima / Prov: Huarochirí / Dist.: San Mateo</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -250,6 +250,141 @@
         <x:is>
           <x:t>VALOR (m³/s)</x:t>
         </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.7224</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.1264</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6603</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8778</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3440</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8623</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3906</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.0376</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.7356</x:v>
       </x:c>
     </x:row>
     <x:row>
